--- a/travel_booking_forms/047_walt_disney_world_vacation_inquiry_form--travel_booking_forms.xlsx
+++ b/travel_booking_forms/047_walt_disney_world_vacation_inquiry_form--travel_booking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1194,8 +1194,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'family',_'value':_'family'}</t>
+          <t>family</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Family', 'value': 'family'}</t>
+          <t>Family</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'couple',_'value':_'couple'}</t>
+          <t>couple</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Couple', 'value': 'couple'}</t>
+          <t>Couple</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'solo',_'value':_'solo'}</t>
+          <t>solo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Solo', 'value': 'solo'}</t>
+          <t>Solo</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'group',_'value':_'group'}</t>
+          <t>group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Group', 'value': 'group'}</t>
+          <t>Group</t>
         </is>
       </c>
     </row>
@@ -1291,12 +1291,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_"disney's_grand_floridian_resort_&amp;_spa",_'value':_'disneys_grand_floridian_resort_and_spa'}</t>
+          <t>disney's_grand_floridian_resort_&amp;_spa</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': "Disney's Grand Floridian Resort &amp; Spa", 'value': 'disneys_grand_floridian_resort_and_spa'}</t>
+          <t>Disney's Grand Floridian Resort &amp; Spa</t>
         </is>
       </c>
     </row>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_"disney's_polynesian_resort",_'value':_'disneys_polynesian_resort'}</t>
+          <t>disney's_polynesian_resort</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': "Disney's Polynesian Resort", 'value': 'disneys_polynesian_resort'}</t>
+          <t>Disney's Polynesian Resort</t>
         </is>
       </c>
     </row>
@@ -1325,12 +1325,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_"disney's_boardwalk",_'value':_'disneys_boardwalk'}</t>
+          <t>disney's_boardwalk</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': "Disney's BoardWalk", 'value': 'disneys_boardwalk'}</t>
+          <t>Disney's BoardWalk</t>
         </is>
       </c>
     </row>
@@ -1342,12 +1342,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1393,12 +1393,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1410,12 +1410,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1427,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'domestic',_'value':_'domestic'}</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Domestic', 'value': 'domestic'}</t>
+          <t>Domestic</t>
         </is>
       </c>
     </row>
@@ -1444,12 +1444,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'international',_'value':_'international'}</t>
+          <t>international</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'International', 'value': 'international'}</t>
+          <t>International</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'national',_'value':_'national'}</t>
+          <t>national</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'National', 'value': 'national'}</t>
+          <t>National</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'florida',_'value':_'florida'}</t>
+          <t>florida</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Florida', 'value': 'florida'}</t>
+          <t>Florida</t>
         </is>
       </c>
     </row>
@@ -1495,12 +1495,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'california',_'value':_'california'}</t>
+          <t>california</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'California', 'value': 'california'}</t>
+          <t>California</t>
         </is>
       </c>
     </row>
@@ -1512,12 +1512,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'orlando_international',_'value':_'orlando_international'}</t>
+          <t>orlando_international</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Orlando International', 'value': 'orlando_international'}</t>
+          <t>Orlando International</t>
         </is>
       </c>
     </row>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'tampa_international',_'value':_'tampa_international'}</t>
+          <t>tampa_international</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Tampa International', 'value': 'tampa_international'}</t>
+          <t>Tampa International</t>
         </is>
       </c>
     </row>
@@ -1563,12 +1563,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1580,12 +1580,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'usd',_'value':_'usd'}</t>
+          <t>usd</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'USD', 'value': 'usd'}</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -1597,12 +1597,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'euro',_'value':_'euro'}</t>
+          <t>euro</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Euro', 'value': 'euro'}</t>
+          <t>Euro</t>
         </is>
       </c>
     </row>
@@ -1614,12 +1614,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1631,12 +1631,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'disney_travel_agency',_'value':_'disney_travel_agency'}</t>
+          <t>disney_travel_agency</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Disney Travel Agency', 'value': 'disney_travel_agency'}</t>
+          <t>Disney Travel Agency</t>
         </is>
       </c>
     </row>
@@ -1648,12 +1648,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'another_agency',_'value':_'another_agency'}</t>
+          <t>another_agency</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Another Agency', 'value': 'another_agency'}</t>
+          <t>Another Agency</t>
         </is>
       </c>
     </row>
@@ -1665,12 +1665,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1682,12 +1682,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1699,12 +1699,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1716,12 +1716,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'usd',_'value':_'usd'}</t>
+          <t>usd</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'USD', 'value': 'usd'}</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -1750,12 +1750,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'euro',_'value':_'euro'}</t>
+          <t>euro</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Euro', 'value': 'euro'}</t>
+          <t>Euro</t>
         </is>
       </c>
     </row>
@@ -1767,12 +1767,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
